--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_1024_run2/epoch_40/per_file_predictions_epoch_40.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_1024_run2/epoch_40/per_file_predictions_epoch_40.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="520">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="523">
   <si>
     <t>Filename</t>
   </si>
@@ -808,772 +808,781 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0,1,0,1</t>
-  </si>
-  <si>
-    <t>0.8437,0.0773,0.0216,0.0495</t>
-  </si>
-  <si>
-    <t>0.0100,0.0022,0.0003,0.9966</t>
-  </si>
-  <si>
-    <t>0.3643,0.0099,0.0062,0.6747</t>
-  </si>
-  <si>
-    <t>0.1638,0.0251,0.0245,0.9049</t>
-  </si>
-  <si>
-    <t>0.9964,0.0003,0.0000,0.0009</t>
-  </si>
-  <si>
-    <t>0.9937,0.0031,0.0001,0.0005</t>
-  </si>
-  <si>
-    <t>0.9769,0.0262,0.0028,0.0006</t>
-  </si>
-  <si>
-    <t>0.9898,0.0034,0.0007,0.0013</t>
-  </si>
-  <si>
-    <t>0.9898,0.0134,0.0003,0.0003</t>
-  </si>
-  <si>
-    <t>0.9894,0.0097,0.0002,0.0005</t>
-  </si>
-  <si>
-    <t>0.9895,0.0068,0.0005,0.0007</t>
-  </si>
-  <si>
-    <t>0.9941,0.0033,0.0002,0.0004</t>
-  </si>
-  <si>
-    <t>0.7071,0.0824,0.2114,0.0036</t>
-  </si>
-  <si>
-    <t>0.3859,0.0198,0.7594,0.0037</t>
-  </si>
-  <si>
-    <t>0.3025,0.0262,0.7968,0.0037</t>
-  </si>
-  <si>
-    <t>0.2108,0.0184,0.8174,0.0165</t>
-  </si>
-  <si>
-    <t>0.6469,0.0814,0.3429,0.0054</t>
-  </si>
-  <si>
-    <t>0.0048,0.9864,0.0181,0.0005</t>
-  </si>
-  <si>
-    <t>0.0016,0.9951,0.0034,0.0003</t>
-  </si>
-  <si>
-    <t>0.0377,0.9458,0.0131,0.0008</t>
-  </si>
-  <si>
-    <t>0.0129,0.9781,0.0055,0.0008</t>
-  </si>
-  <si>
-    <t>0.0025,0.9937,0.0041,0.0001</t>
-  </si>
-  <si>
-    <t>0.1662,0.0660,0.7316,0.0721</t>
-  </si>
-  <si>
-    <t>0.6377,0.0050,0.5175,0.0033</t>
-  </si>
-  <si>
-    <t>0.0050,0.0040,0.9924,0.0017</t>
-  </si>
-  <si>
-    <t>0.4070,0.0186,0.6860,0.0182</t>
-  </si>
-  <si>
-    <t>0.0289,0.0046,0.9742,0.0022</t>
-  </si>
-  <si>
-    <t>0.0664,0.0045,0.9424,0.0060</t>
-  </si>
-  <si>
-    <t>0.0075,0.0021,0.9860,0.0082</t>
-  </si>
-  <si>
-    <t>0.6606,0.2770,0.0278,0.0002</t>
-  </si>
-  <si>
-    <t>0.3862,0.0781,0.6303,0.0053</t>
-  </si>
-  <si>
-    <t>0.0006,0.0053,0.9975,0.0017</t>
-  </si>
-  <si>
-    <t>0.0673,0.8069,0.2661,0.0101</t>
-  </si>
-  <si>
-    <t>0.8532,0.0646,0.0845,0.0071</t>
-  </si>
-  <si>
-    <t>0.8151,0.1282,0.0643,0.0034</t>
-  </si>
-  <si>
-    <t>0.5953,0.5689,0.0042,0.0007</t>
-  </si>
-  <si>
-    <t>0.0244,0.9366,0.1464,0.0046</t>
-  </si>
-  <si>
-    <t>0.0153,0.7248,0.5167,0.0321</t>
-  </si>
-  <si>
-    <t>0.0138,0.1166,0.9314,0.0274</t>
-  </si>
-  <si>
-    <t>0.0419,0.5670,0.6926,0.0140</t>
-  </si>
-  <si>
-    <t>0.0298,0.0118,0.8900,0.1050</t>
-  </si>
-  <si>
-    <t>0.0082,0.3998,0.9433,0.0031</t>
-  </si>
-  <si>
-    <t>0.0051,0.9846,0.0049,0.0004</t>
-  </si>
-  <si>
-    <t>0.0659,0.0224,0.8988,0.0161</t>
-  </si>
-  <si>
-    <t>0.0767,0.5480,0.0231,0.8534</t>
-  </si>
-  <si>
-    <t>0.0017,0.9848,0.0079,0.0151</t>
-  </si>
-  <si>
-    <t>0.0011,0.9902,0.0242,0.0024</t>
-  </si>
-  <si>
-    <t>0.0017,0.9845,0.0157,0.0103</t>
-  </si>
-  <si>
-    <t>0.0189,0.5368,0.8088,0.0029</t>
-  </si>
-  <si>
-    <t>0.0066,0.1351,0.9744,0.0013</t>
-  </si>
-  <si>
-    <t>0.0238,0.0156,0.9664,0.0070</t>
-  </si>
-  <si>
-    <t>0.0539,0.0033,0.9716,0.0015</t>
-  </si>
-  <si>
-    <t>0.0157,0.1408,0.9008,0.0186</t>
-  </si>
-  <si>
-    <t>0.0292,0.5215,0.7074,0.0032</t>
-  </si>
-  <si>
-    <t>0.8777,0.1607,0.0107,0.0025</t>
-  </si>
-  <si>
-    <t>0.7855,0.1117,0.1294,0.0031</t>
-  </si>
-  <si>
-    <t>0.9488,0.0547,0.0079,0.0016</t>
-  </si>
-  <si>
-    <t>0.0047,0.0430,0.9876,0.0042</t>
-  </si>
-  <si>
-    <t>0.9790,0.0157,0.0016,0.0012</t>
-  </si>
-  <si>
-    <t>0.9322,0.0942,0.0065,0.0013</t>
-  </si>
-  <si>
-    <t>0.5254,0.5015,0.0747,0.0108</t>
-  </si>
-  <si>
-    <t>0.0024,0.8765,0.8474,0.0009</t>
-  </si>
-  <si>
-    <t>0.0585,0.0387,0.9084,0.0227</t>
-  </si>
-  <si>
-    <t>0.0035,0.0457,0.9737,0.0090</t>
-  </si>
-  <si>
-    <t>0.0005,0.9818,0.5878,0.0004</t>
-  </si>
-  <si>
-    <t>0.0094,0.0100,0.9720,0.0190</t>
-  </si>
-  <si>
-    <t>0.0362,0.9167,0.0697,0.0015</t>
-  </si>
-  <si>
-    <t>0.0021,0.9970,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.4702,0.0619,0.6329,0.0013</t>
-  </si>
-  <si>
-    <t>0.0265,0.4997,0.8575,0.0035</t>
-  </si>
-  <si>
-    <t>0.0271,0.0266,0.9781,0.0005</t>
-  </si>
-  <si>
-    <t>0.0101,0.8887,0.4996,0.0023</t>
-  </si>
-  <si>
-    <t>0.0106,0.7038,0.7211,0.0013</t>
-  </si>
-  <si>
-    <t>0.0035,0.9843,0.0308,0.0002</t>
-  </si>
-  <si>
-    <t>0.0061,0.8466,0.7600,0.0004</t>
-  </si>
-  <si>
-    <t>0.0604,0.0076,0.2052,0.8267</t>
-  </si>
-  <si>
-    <t>0.0023,0.0471,0.0003,0.9979</t>
-  </si>
-  <si>
-    <t>0.0010,0.0465,0.0005,0.9983</t>
-  </si>
-  <si>
-    <t>0.0226,0.0060,0.0028,0.9870</t>
-  </si>
-  <si>
-    <t>0.0156,0.0075,0.0038,0.9889</t>
-  </si>
-  <si>
-    <t>0.0262,0.0141,0.0096,0.9777</t>
-  </si>
-  <si>
-    <t>0.0024,0.9517,0.4972,0.0024</t>
-  </si>
-  <si>
-    <t>0.0079,0.8226,0.8429,0.0010</t>
-  </si>
-  <si>
-    <t>0.0083,0.9375,0.1705,0.0060</t>
-  </si>
-  <si>
-    <t>0.0036,0.9318,0.4107,0.0086</t>
-  </si>
-  <si>
-    <t>0.0048,0.9601,0.2196,0.0020</t>
-  </si>
-  <si>
-    <t>0.0059,0.8763,0.7207,0.0016</t>
-  </si>
-  <si>
-    <t>0.9841,0.0106,0.0022,0.0008</t>
-  </si>
-  <si>
-    <t>0.8727,0.1648,0.0134,0.0010</t>
-  </si>
-  <si>
-    <t>0.9736,0.0224,0.0046,0.0009</t>
-  </si>
-  <si>
-    <t>0.9775,0.0134,0.0013,0.0023</t>
-  </si>
-  <si>
-    <t>0.9860,0.0088,0.0017,0.0008</t>
-  </si>
-  <si>
-    <t>0.9762,0.0225,0.0027,0.0012</t>
-  </si>
-  <si>
-    <t>0.8657,0.1555,0.0185,0.0023</t>
-  </si>
-  <si>
-    <t>0.9250,0.1087,0.0028,0.0019</t>
-  </si>
-  <si>
-    <t>0.9955,0.0010,0.0001,0.0008</t>
-  </si>
-  <si>
-    <t>0.9834,0.0177,0.0021,0.0003</t>
-  </si>
-  <si>
-    <t>0.9814,0.0197,0.0012,0.0009</t>
-  </si>
-  <si>
-    <t>0.9886,0.0087,0.0013,0.0005</t>
-  </si>
-  <si>
-    <t>0.9763,0.0160,0.0027,0.0021</t>
-  </si>
-  <si>
-    <t>0.9608,0.0444,0.0039,0.0025</t>
-  </si>
-  <si>
-    <t>0.9880,0.0096,0.0007,0.0009</t>
-  </si>
-  <si>
-    <t>0.9936,0.0012,0.0002,0.0014</t>
-  </si>
-  <si>
-    <t>0.0125,0.0102,0.9789,0.0067</t>
-  </si>
-  <si>
-    <t>0.0391,0.0031,0.9785,0.0013</t>
-  </si>
-  <si>
-    <t>0.6438,0.0196,0.4715,0.0069</t>
-  </si>
-  <si>
-    <t>0.0451,0.0051,0.9624,0.0026</t>
-  </si>
-  <si>
-    <t>0.0189,0.9687,0.0037,0.0006</t>
-  </si>
-  <si>
-    <t>0.0067,0.9835,0.0090,0.0010</t>
-  </si>
-  <si>
-    <t>0.0449,0.9388,0.0055,0.0042</t>
-  </si>
-  <si>
-    <t>0.0504,0.9316,0.0118,0.0015</t>
-  </si>
-  <si>
-    <t>0.0047,0.9878,0.0019,0.0010</t>
-  </si>
-  <si>
-    <t>0.0106,0.9834,0.0039,0.0003</t>
-  </si>
-  <si>
-    <t>0.1170,0.8752,0.0145,0.0018</t>
-  </si>
-  <si>
-    <t>0.6402,0.1373,0.2457,0.0140</t>
-  </si>
-  <si>
-    <t>0.2027,0.0414,0.7711,0.0409</t>
-  </si>
-  <si>
-    <t>0.5713,0.0966,0.3649,0.0123</t>
-  </si>
-  <si>
-    <t>0.1691,0.3335,0.5534,0.0157</t>
-  </si>
-  <si>
-    <t>0.1138,0.0500,0.0301,0.9062</t>
-  </si>
-  <si>
-    <t>0.0005,0.9967,0.0056,0.0004</t>
-  </si>
-  <si>
-    <t>0.0002,0.9943,0.0011,0.0508</t>
-  </si>
-  <si>
-    <t>0.0078,0.9466,0.0401,0.1073</t>
-  </si>
-  <si>
-    <t>0.0019,0.9831,0.1344,0.0004</t>
-  </si>
-  <si>
-    <t>0.0032,0.9909,0.0203,0.0001</t>
-  </si>
-  <si>
-    <t>0.5505,0.4362,0.0504,0.0008</t>
-  </si>
-  <si>
-    <t>0.2175,0.7990,0.0247,0.0008</t>
-  </si>
-  <si>
-    <t>0.9008,0.1027,0.0192,0.0018</t>
-  </si>
-  <si>
-    <t>0.9812,0.0096,0.0023,0.0030</t>
-  </si>
-  <si>
-    <t>0.9581,0.0315,0.0131,0.0018</t>
-  </si>
-  <si>
-    <t>0.9440,0.0271,0.0294,0.0035</t>
-  </si>
-  <si>
-    <t>0.9911,0.0058,0.0009,0.0005</t>
-  </si>
-  <si>
-    <t>0.8147,0.1698,0.0603,0.0060</t>
-  </si>
-  <si>
-    <t>0.9615,0.0136,0.0044,0.0072</t>
-  </si>
-  <si>
-    <t>0.9812,0.0057,0.0057,0.0017</t>
-  </si>
-  <si>
-    <t>0.0080,0.8482,0.6665,0.0021</t>
-  </si>
-  <si>
-    <t>0.0048,0.2918,0.9507,0.0018</t>
-  </si>
-  <si>
-    <t>0.0606,0.1372,0.8410,0.0102</t>
-  </si>
-  <si>
-    <t>0.0279,0.1501,0.9024,0.0006</t>
-  </si>
-  <si>
-    <t>0.8615,0.0278,0.0947,0.0047</t>
-  </si>
-  <si>
-    <t>0.7122,0.0294,0.3595,0.0097</t>
-  </si>
-  <si>
-    <t>0.2842,0.0026,0.8058,0.0204</t>
-  </si>
-  <si>
-    <t>0.6388,0.0850,0.2971,0.0447</t>
-  </si>
-  <si>
-    <t>0.0721,0.0019,0.0026,0.9714</t>
-  </si>
-  <si>
-    <t>0.0017,0.0004,0.0045,0.9955</t>
-  </si>
-  <si>
-    <t>0.0097,0.0038,0.0038,0.9914</t>
-  </si>
-  <si>
-    <t>0.0270,0.0032,0.0029,0.9867</t>
-  </si>
-  <si>
-    <t>0.0053,0.9332,0.5264,0.0024</t>
-  </si>
-  <si>
-    <t>0.8484,0.2123,0.0076,0.0046</t>
-  </si>
-  <si>
-    <t>0.1841,0.8010,0.0413,0.0052</t>
-  </si>
-  <si>
-    <t>0.9624,0.0157,0.0022,0.0087</t>
-  </si>
-  <si>
-    <t>0.7236,0.3316,0.0262,0.0061</t>
-  </si>
-  <si>
-    <t>0.9367,0.0463,0.0182,0.0029</t>
-  </si>
-  <si>
-    <t>0.6176,0.0092,0.1454,0.2038</t>
-  </si>
-  <si>
-    <t>0.9661,0.0106,0.0078,0.0061</t>
-  </si>
-  <si>
-    <t>0.0221,0.0364,0.9215,0.0750</t>
-  </si>
-  <si>
-    <t>0.5217,0.0009,0.0024,0.6472</t>
-  </si>
-  <si>
-    <t>0.9383,0.0030,0.0090,0.0195</t>
-  </si>
-  <si>
-    <t>0.1066,0.8547,0.0404,0.0043</t>
-  </si>
-  <si>
-    <t>0.7901,0.1514,0.0522,0.0029</t>
-  </si>
-  <si>
-    <t>0.7986,0.1956,0.0357,0.0082</t>
-  </si>
-  <si>
-    <t>0.1402,0.7893,0.0647,0.0069</t>
-  </si>
-  <si>
-    <t>0.6118,0.2709,0.1349,0.0041</t>
-  </si>
-  <si>
-    <t>0.7355,0.1946,0.1047,0.0112</t>
-  </si>
-  <si>
-    <t>0.9619,0.0359,0.0081,0.0013</t>
-  </si>
-  <si>
-    <t>0.9865,0.0101,0.0006,0.0012</t>
-  </si>
-  <si>
-    <t>0.9899,0.0081,0.0015,0.0002</t>
-  </si>
-  <si>
-    <t>0.9738,0.0076,0.0031,0.0070</t>
-  </si>
-  <si>
-    <t>0.9706,0.0207,0.0090,0.0011</t>
-  </si>
-  <si>
-    <t>0.9719,0.0205,0.0009,0.0022</t>
-  </si>
-  <si>
-    <t>0.9850,0.0037,0.0011,0.0040</t>
-  </si>
-  <si>
-    <t>0.9856,0.0079,0.0027,0.0010</t>
-  </si>
-  <si>
-    <t>0.1538,0.8059,0.0292,0.0067</t>
-  </si>
-  <si>
-    <t>0.5157,0.6375,0.0060,0.0029</t>
-  </si>
-  <si>
-    <t>0.3692,0.7638,0.0033,0.0005</t>
-  </si>
-  <si>
-    <t>0.6963,0.2710,0.0700,0.0112</t>
-  </si>
-  <si>
-    <t>0.9485,0.0608,0.0036,0.0012</t>
-  </si>
-  <si>
-    <t>0.8071,0.1955,0.0308,0.0032</t>
-  </si>
-  <si>
-    <t>0.9338,0.1128,0.0034,0.0005</t>
-  </si>
-  <si>
-    <t>0.7957,0.1259,0.1041,0.0023</t>
-  </si>
-  <si>
-    <t>0.0069,0.0367,0.9888,0.0012</t>
-  </si>
-  <si>
-    <t>0.9328,0.0977,0.0044,0.0014</t>
-  </si>
-  <si>
-    <t>0.0895,0.0102,0.9470,0.0008</t>
-  </si>
-  <si>
-    <t>0.0015,0.0638,0.9910,0.0020</t>
-  </si>
-  <si>
-    <t>0.0336,0.0072,0.9715,0.0036</t>
-  </si>
-  <si>
-    <t>0.0043,0.3446,0.9734,0.0006</t>
-  </si>
-  <si>
-    <t>0.0051,0.0121,0.9917,0.0016</t>
-  </si>
-  <si>
-    <t>0.0049,0.0006,0.9968,0.0002</t>
-  </si>
-  <si>
-    <t>0.0471,0.0200,0.9582,0.0025</t>
-  </si>
-  <si>
-    <t>0.4732,0.0577,0.5720,0.0025</t>
-  </si>
-  <si>
-    <t>0.2581,0.0249,0.6945,0.0980</t>
-  </si>
-  <si>
-    <t>0.3130,0.0999,0.6278,0.0259</t>
-  </si>
-  <si>
-    <t>0.1377,0.6886,0.1937,0.0041</t>
-  </si>
-  <si>
-    <t>0.1007,0.0665,0.8665,0.0024</t>
-  </si>
-  <si>
-    <t>0.6259,0.0518,0.3916,0.0077</t>
-  </si>
-  <si>
-    <t>0.6317,0.1021,0.2186,0.0812</t>
-  </si>
-  <si>
-    <t>0.3304,0.1147,0.5867,0.0211</t>
-  </si>
-  <si>
-    <t>0.7065,0.4069,0.0127,0.0043</t>
-  </si>
-  <si>
-    <t>0.1889,0.8471,0.0045,0.0042</t>
-  </si>
-  <si>
-    <t>0.1650,0.8344,0.0345,0.0029</t>
-  </si>
-  <si>
-    <t>0.8508,0.2301,0.0079,0.0025</t>
-  </si>
-  <si>
-    <t>0.7429,0.3007,0.0249,0.0036</t>
-  </si>
-  <si>
-    <t>0.3413,0.4407,0.2653,0.0904</t>
-  </si>
-  <si>
-    <t>0.8013,0.0083,0.2803,0.0040</t>
-  </si>
-  <si>
-    <t>0.7188,0.0222,0.3141,0.0236</t>
-  </si>
-  <si>
-    <t>0.7094,0.0039,0.5051,0.0021</t>
-  </si>
-  <si>
-    <t>0.8190,0.0024,0.1626,0.0204</t>
-  </si>
-  <si>
-    <t>0.0199,0.0453,0.9572,0.0147</t>
-  </si>
-  <si>
-    <t>0.0682,0.0628,0.8858,0.0244</t>
-  </si>
-  <si>
-    <t>0.0506,0.2832,0.5900,0.1276</t>
-  </si>
-  <si>
-    <t>0.0984,0.1349,0.8219,0.0082</t>
-  </si>
-  <si>
-    <t>0.0357,0.0988,0.8988,0.0281</t>
-  </si>
-  <si>
-    <t>0.9916,0.0022,0.0002,0.0015</t>
-  </si>
-  <si>
-    <t>0.9775,0.0189,0.0020,0.0014</t>
-  </si>
-  <si>
-    <t>0.9352,0.0998,0.0040,0.0016</t>
-  </si>
-  <si>
-    <t>0.9453,0.0591,0.0078,0.0015</t>
-  </si>
-  <si>
-    <t>0.9665,0.0326,0.0029,0.0016</t>
-  </si>
-  <si>
-    <t>0.9750,0.0174,0.0049,0.0020</t>
-  </si>
-  <si>
-    <t>0.9717,0.0295,0.0059,0.0004</t>
-  </si>
-  <si>
-    <t>0.9921,0.0037,0.0009,0.0006</t>
-  </si>
-  <si>
-    <t>0.1788,0.0201,0.8646,0.0163</t>
-  </si>
-  <si>
-    <t>0.5610,0.1017,0.4230,0.0276</t>
-  </si>
-  <si>
-    <t>0.8538,0.0342,0.0614,0.0361</t>
-  </si>
-  <si>
-    <t>0.0212,0.0238,0.9660,0.0035</t>
-  </si>
-  <si>
-    <t>0.0015,0.0036,0.9953,0.0026</t>
-  </si>
-  <si>
-    <t>0.0200,0.0079,0.9759,0.0020</t>
-  </si>
-  <si>
-    <t>0.0002,0.0010,0.9977,0.0041</t>
-  </si>
-  <si>
-    <t>0.0515,0.3294,0.6687,0.0189</t>
-  </si>
-  <si>
-    <t>0.0002,0.0050,0.9992,0.0002</t>
-  </si>
-  <si>
-    <t>0.0109,0.0654,0.9312,0.0196</t>
-  </si>
-  <si>
-    <t>0.3438,0.0177,0.7443,0.0099</t>
-  </si>
-  <si>
-    <t>0.6449,0.0123,0.4425,0.0166</t>
-  </si>
-  <si>
-    <t>0.5999,0.0052,0.1568,0.2114</t>
-  </si>
-  <si>
-    <t>0.7848,0.0045,0.3277,0.0047</t>
-  </si>
-  <si>
-    <t>0.9254,0.0733,0.0125,0.0022</t>
-  </si>
-  <si>
-    <t>0.9661,0.0481,0.0024,0.0006</t>
-  </si>
-  <si>
-    <t>0.9901,0.0075,0.0007,0.0007</t>
-  </si>
-  <si>
-    <t>0.9896,0.0086,0.0008,0.0005</t>
-  </si>
-  <si>
-    <t>0.9469,0.0612,0.0070,0.0006</t>
-  </si>
-  <si>
-    <t>0.9646,0.0434,0.0039,0.0005</t>
-  </si>
-  <si>
-    <t>0.9821,0.0087,0.0002,0.0015</t>
-  </si>
-  <si>
-    <t>0.9764,0.0138,0.0033,0.0022</t>
-  </si>
-  <si>
-    <t>0.0106,0.0048,0.9893,0.0007</t>
-  </si>
-  <si>
-    <t>0.0031,0.3670,0.9031,0.0078</t>
-  </si>
-  <si>
-    <t>0.0131,0.1509,0.9143,0.0063</t>
-  </si>
-  <si>
-    <t>0.0841,0.3794,0.5829,0.0194</t>
-  </si>
-  <si>
-    <t>0.0057,0.0032,0.9818,0.0140</t>
-  </si>
-  <si>
-    <t>0.0858,0.0017,0.8145,0.0969</t>
-  </si>
-  <si>
-    <t>0.0861,0.0194,0.9102,0.0171</t>
-  </si>
-  <si>
-    <t>0.0217,0.0350,0.9098,0.0741</t>
-  </si>
-  <si>
-    <t>0.4341,0.0008,0.0148,0.6464</t>
-  </si>
-  <si>
-    <t>0.0038,0.0111,0.0020,0.9953</t>
-  </si>
-  <si>
-    <t>0.1026,0.0071,0.0012,0.9633</t>
-  </si>
-  <si>
-    <t>0.0237,0.0009,0.0013,0.9904</t>
-  </si>
-  <si>
-    <t>0.0042,0.0003,0.0003,0.9982</t>
-  </si>
-  <si>
-    <t>0.2159,0.3045,0.1005,0.6845</t>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>1,0,1,0</t>
+  </si>
+  <si>
+    <t>1,1,0,0</t>
+  </si>
+  <si>
+    <t>1,0,0,1</t>
+  </si>
+  <si>
+    <t>0.4666,0.1204,0.0295,0.4245</t>
+  </si>
+  <si>
+    <t>0.0192,0.0092,0.0015,0.9906</t>
+  </si>
+  <si>
+    <t>0.7931,0.0264,0.0834,0.0611</t>
+  </si>
+  <si>
+    <t>0.1068,0.0033,0.0051,0.9562</t>
+  </si>
+  <si>
+    <t>0.9969,0.0012,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9857,0.0103,0.0007,0.0009</t>
+  </si>
+  <si>
+    <t>0.9848,0.0118,0.0035,0.0005</t>
+  </si>
+  <si>
+    <t>0.9943,0.0006,0.0003,0.0013</t>
+  </si>
+  <si>
+    <t>0.9845,0.0111,0.0021,0.0008</t>
+  </si>
+  <si>
+    <t>0.9745,0.0318,0.0020,0.0005</t>
+  </si>
+  <si>
+    <t>0.9860,0.0150,0.0010,0.0005</t>
+  </si>
+  <si>
+    <t>0.9953,0.0017,0.0002,0.0004</t>
+  </si>
+  <si>
+    <t>0.5845,0.0203,0.5616,0.0125</t>
+  </si>
+  <si>
+    <t>0.1319,0.1248,0.7990,0.0032</t>
+  </si>
+  <si>
+    <t>0.2548,0.0285,0.8227,0.0048</t>
+  </si>
+  <si>
+    <t>0.0383,0.0150,0.9605,0.0038</t>
+  </si>
+  <si>
+    <t>0.7070,0.0267,0.2435,0.0475</t>
+  </si>
+  <si>
+    <t>0.0038,0.9895,0.0052,0.0007</t>
+  </si>
+  <si>
+    <t>0.0053,0.9895,0.0074,0.0001</t>
+  </si>
+  <si>
+    <t>0.0645,0.9172,0.0101,0.0013</t>
+  </si>
+  <si>
+    <t>0.0045,0.9920,0.0008,0.0008</t>
+  </si>
+  <si>
+    <t>0.0062,0.9836,0.0200,0.0003</t>
+  </si>
+  <si>
+    <t>0.5295,0.0036,0.6594,0.0050</t>
+  </si>
+  <si>
+    <t>0.5120,0.0033,0.5353,0.0251</t>
+  </si>
+  <si>
+    <t>0.0719,0.0032,0.9583,0.0022</t>
+  </si>
+  <si>
+    <t>0.1315,0.0053,0.8928,0.0150</t>
+  </si>
+  <si>
+    <t>0.0309,0.0163,0.9591,0.0098</t>
+  </si>
+  <si>
+    <t>0.0702,0.0209,0.9040,0.0120</t>
+  </si>
+  <si>
+    <t>0.0030,0.0011,0.9855,0.0201</t>
+  </si>
+  <si>
+    <t>0.1713,0.8242,0.0222,0.0028</t>
+  </si>
+  <si>
+    <t>0.3628,0.2137,0.5394,0.0290</t>
+  </si>
+  <si>
+    <t>0.0106,0.0478,0.9769,0.0074</t>
+  </si>
+  <si>
+    <t>0.0416,0.8828,0.1370,0.0010</t>
+  </si>
+  <si>
+    <t>0.6203,0.3170,0.0221,0.0491</t>
+  </si>
+  <si>
+    <t>0.7114,0.1617,0.1066,0.0033</t>
+  </si>
+  <si>
+    <t>0.6389,0.4433,0.0219,0.0018</t>
+  </si>
+  <si>
+    <t>0.0439,0.9295,0.0577,0.0023</t>
+  </si>
+  <si>
+    <t>0.0115,0.3397,0.9188,0.0046</t>
+  </si>
+  <si>
+    <t>0.0268,0.5101,0.8898,0.0155</t>
+  </si>
+  <si>
+    <t>0.0211,0.2330,0.9251,0.0035</t>
+  </si>
+  <si>
+    <t>0.0314,0.0016,0.5918,0.4116</t>
+  </si>
+  <si>
+    <t>0.0356,0.2657,0.8691,0.0038</t>
+  </si>
+  <si>
+    <t>0.0022,0.9866,0.0125,0.0023</t>
+  </si>
+  <si>
+    <t>0.0271,0.0146,0.9565,0.0105</t>
+  </si>
+  <si>
+    <t>0.2651,0.1933,0.0086,0.6011</t>
+  </si>
+  <si>
+    <t>0.0096,0.9675,0.0299,0.0098</t>
+  </si>
+  <si>
+    <t>0.0020,0.9886,0.0257,0.0014</t>
+  </si>
+  <si>
+    <t>0.0019,0.9890,0.0168,0.0025</t>
+  </si>
+  <si>
+    <t>0.0405,0.2304,0.8929,0.0130</t>
+  </si>
+  <si>
+    <t>0.0014,0.0428,0.9945,0.0007</t>
+  </si>
+  <si>
+    <t>0.0673,0.0095,0.9233,0.0159</t>
+  </si>
+  <si>
+    <t>0.0196,0.0020,0.9816,0.0037</t>
+  </si>
+  <si>
+    <t>0.0092,0.0639,0.9812,0.0008</t>
+  </si>
+  <si>
+    <t>0.0104,0.0044,0.9908,0.0003</t>
+  </si>
+  <si>
+    <t>0.8340,0.2438,0.0086,0.0013</t>
+  </si>
+  <si>
+    <t>0.9016,0.0877,0.0335,0.0039</t>
+  </si>
+  <si>
+    <t>0.9547,0.0322,0.0048,0.0037</t>
+  </si>
+  <si>
+    <t>0.0208,0.0487,0.9744,0.0042</t>
+  </si>
+  <si>
+    <t>0.9646,0.0184,0.0068,0.0027</t>
+  </si>
+  <si>
+    <t>0.9211,0.1035,0.0088,0.0016</t>
+  </si>
+  <si>
+    <t>0.9844,0.0065,0.0015,0.0021</t>
+  </si>
+  <si>
+    <t>0.0159,0.7727,0.7208,0.0054</t>
+  </si>
+  <si>
+    <t>0.0060,0.1660,0.9487,0.0037</t>
+  </si>
+  <si>
+    <t>0.0029,0.0809,0.9797,0.0029</t>
+  </si>
+  <si>
+    <t>0.0005,0.9160,0.9501,0.0001</t>
+  </si>
+  <si>
+    <t>0.0068,0.0049,0.9832,0.0101</t>
+  </si>
+  <si>
+    <t>0.0409,0.9198,0.0495,0.0020</t>
+  </si>
+  <si>
+    <t>0.0078,0.9925,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.7327,0.0877,0.2299,0.0082</t>
+  </si>
+  <si>
+    <t>0.3247,0.1264,0.6780,0.0161</t>
+  </si>
+  <si>
+    <t>0.2307,0.2526,0.2955,0.0004</t>
+  </si>
+  <si>
+    <t>0.0081,0.8466,0.6618,0.0029</t>
+  </si>
+  <si>
+    <t>0.0065,0.8814,0.5960,0.0034</t>
+  </si>
+  <si>
+    <t>0.0049,0.9719,0.1020,0.0008</t>
+  </si>
+  <si>
+    <t>0.0003,0.9776,0.8688,0.0001</t>
+  </si>
+  <si>
+    <t>0.0596,0.0100,0.0539,0.9295</t>
+  </si>
+  <si>
+    <t>0.0084,0.0091,0.0016,0.9945</t>
+  </si>
+  <si>
+    <t>0.0189,0.0031,0.0032,0.9869</t>
+  </si>
+  <si>
+    <t>0.0268,0.0042,0.0038,0.9852</t>
+  </si>
+  <si>
+    <t>0.0461,0.0081,0.0122,0.9677</t>
+  </si>
+  <si>
+    <t>0.0873,0.0100,0.0083,0.9525</t>
+  </si>
+  <si>
+    <t>0.0037,0.9611,0.3425,0.0015</t>
+  </si>
+  <si>
+    <t>0.0057,0.2992,0.9709,0.0011</t>
+  </si>
+  <si>
+    <t>0.0406,0.8660,0.1479,0.0106</t>
+  </si>
+  <si>
+    <t>0.0055,0.6941,0.6376,0.0086</t>
+  </si>
+  <si>
+    <t>0.0022,0.9611,0.3548,0.0002</t>
+  </si>
+  <si>
+    <t>0.0158,0.4481,0.8942,0.0032</t>
+  </si>
+  <si>
+    <t>0.9696,0.0352,0.0025,0.0010</t>
+  </si>
+  <si>
+    <t>0.8681,0.1873,0.0101,0.0012</t>
+  </si>
+  <si>
+    <t>0.7885,0.3077,0.0122,0.0016</t>
+  </si>
+  <si>
+    <t>0.9832,0.0124,0.0016,0.0009</t>
+  </si>
+  <si>
+    <t>0.9623,0.0395,0.0059,0.0022</t>
+  </si>
+  <si>
+    <t>0.9513,0.0624,0.0056,0.0013</t>
+  </si>
+  <si>
+    <t>0.9780,0.0224,0.0023,0.0010</t>
+  </si>
+  <si>
+    <t>0.9761,0.0214,0.0005,0.0015</t>
+  </si>
+  <si>
+    <t>0.9889,0.0033,0.0021,0.0013</t>
+  </si>
+  <si>
+    <t>0.9914,0.0083,0.0004,0.0003</t>
+  </si>
+  <si>
+    <t>0.9918,0.0059,0.0004,0.0005</t>
+  </si>
+  <si>
+    <t>0.9970,0.0009,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9797,0.0172,0.0014,0.0016</t>
+  </si>
+  <si>
+    <t>0.9218,0.0962,0.0047,0.0028</t>
+  </si>
+  <si>
+    <t>0.9814,0.0138,0.0014,0.0015</t>
+  </si>
+  <si>
+    <t>0.9936,0.0028,0.0005,0.0006</t>
+  </si>
+  <si>
+    <t>0.0082,0.0018,0.9912,0.0017</t>
+  </si>
+  <si>
+    <t>0.0498,0.0620,0.9192,0.0017</t>
+  </si>
+  <si>
+    <t>0.3465,0.0706,0.6230,0.0337</t>
+  </si>
+  <si>
+    <t>0.0676,0.0082,0.9218,0.0240</t>
+  </si>
+  <si>
+    <t>0.0148,0.9757,0.0021,0.0011</t>
+  </si>
+  <si>
+    <t>0.0149,0.9788,0.0027,0.0004</t>
+  </si>
+  <si>
+    <t>0.0495,0.9390,0.0062,0.0026</t>
+  </si>
+  <si>
+    <t>0.0605,0.9190,0.0163,0.0037</t>
+  </si>
+  <si>
+    <t>0.0585,0.9367,0.0053,0.0012</t>
+  </si>
+  <si>
+    <t>0.0056,0.9889,0.0014,0.0005</t>
+  </si>
+  <si>
+    <t>0.1683,0.8364,0.0263,0.0029</t>
+  </si>
+  <si>
+    <t>0.5283,0.2196,0.2946,0.0108</t>
+  </si>
+  <si>
+    <t>0.1821,0.0419,0.8281,0.0027</t>
+  </si>
+  <si>
+    <t>0.2438,0.4655,0.2945,0.0888</t>
+  </si>
+  <si>
+    <t>0.5843,0.0535,0.4368,0.0053</t>
+  </si>
+  <si>
+    <t>0.2516,0.0923,0.1316,0.6246</t>
+  </si>
+  <si>
+    <t>0.0018,0.9909,0.0195,0.0004</t>
+  </si>
+  <si>
+    <t>0.0008,0.9900,0.0025,0.0123</t>
+  </si>
+  <si>
+    <t>0.0207,0.8744,0.0936,0.2060</t>
+  </si>
+  <si>
+    <t>0.0036,0.9822,0.0444,0.0013</t>
+  </si>
+  <si>
+    <t>0.0109,0.9762,0.0426,0.0004</t>
+  </si>
+  <si>
+    <t>0.6869,0.3409,0.0378,0.0014</t>
+  </si>
+  <si>
+    <t>0.2208,0.8203,0.0212,0.0013</t>
+  </si>
+  <si>
+    <t>0.9639,0.0357,0.0049,0.0007</t>
+  </si>
+  <si>
+    <t>0.9810,0.0019,0.0002,0.0080</t>
+  </si>
+  <si>
+    <t>0.9816,0.0012,0.0006,0.0086</t>
+  </si>
+  <si>
+    <t>0.9617,0.0263,0.0088,0.0026</t>
+  </si>
+  <si>
+    <t>0.9806,0.0087,0.0052,0.0017</t>
+  </si>
+  <si>
+    <t>0.9547,0.0202,0.0133,0.0054</t>
+  </si>
+  <si>
+    <t>0.9582,0.0178,0.0099,0.0075</t>
+  </si>
+  <si>
+    <t>0.9839,0.0085,0.0019,0.0015</t>
+  </si>
+  <si>
+    <t>0.0016,0.9247,0.7576,0.0004</t>
+  </si>
+  <si>
+    <t>0.0153,0.6551,0.8156,0.0025</t>
+  </si>
+  <si>
+    <t>0.0959,0.4940,0.5881,0.0320</t>
+  </si>
+  <si>
+    <t>0.0203,0.0852,0.9457,0.0018</t>
+  </si>
+  <si>
+    <t>0.7469,0.0159,0.1963,0.0299</t>
+  </si>
+  <si>
+    <t>0.2499,0.1891,0.6113,0.0557</t>
+  </si>
+  <si>
+    <t>0.4295,0.0140,0.7770,0.0028</t>
+  </si>
+  <si>
+    <t>0.5647,0.0916,0.4220,0.0175</t>
+  </si>
+  <si>
+    <t>0.0958,0.0162,0.0828,0.8722</t>
+  </si>
+  <si>
+    <t>0.0008,0.0002,0.0037,0.9969</t>
+  </si>
+  <si>
+    <t>0.0007,0.0406,0.0028,0.9970</t>
+  </si>
+  <si>
+    <t>0.0140,0.0013,0.0036,0.9902</t>
+  </si>
+  <si>
+    <t>0.0108,0.8985,0.3928,0.0066</t>
+  </si>
+  <si>
+    <t>0.9416,0.0685,0.0072,0.0010</t>
+  </si>
+  <si>
+    <t>0.4617,0.6465,0.0127,0.0020</t>
+  </si>
+  <si>
+    <t>0.9757,0.0072,0.0016,0.0063</t>
+  </si>
+  <si>
+    <t>0.4452,0.6571,0.0185,0.0026</t>
+  </si>
+  <si>
+    <t>0.9458,0.0057,0.0045,0.0253</t>
+  </si>
+  <si>
+    <t>0.2249,0.0123,0.0502,0.8260</t>
+  </si>
+  <si>
+    <t>0.9778,0.0141,0.0021,0.0015</t>
+  </si>
+  <si>
+    <t>0.0105,0.1062,0.9382,0.0360</t>
+  </si>
+  <si>
+    <t>0.4437,0.0022,0.0074,0.6876</t>
+  </si>
+  <si>
+    <t>0.8615,0.0052,0.0156,0.0881</t>
+  </si>
+  <si>
+    <t>0.1096,0.8128,0.1309,0.0104</t>
+  </si>
+  <si>
+    <t>0.8909,0.0582,0.0336,0.0035</t>
+  </si>
+  <si>
+    <t>0.9284,0.0291,0.0198,0.0051</t>
+  </si>
+  <si>
+    <t>0.0849,0.8286,0.0381,0.0183</t>
+  </si>
+  <si>
+    <t>0.3506,0.3214,0.4421,0.0188</t>
+  </si>
+  <si>
+    <t>0.7875,0.1222,0.0917,0.0023</t>
+  </si>
+  <si>
+    <t>0.9809,0.0070,0.0018,0.0038</t>
+  </si>
+  <si>
+    <t>0.9620,0.0330,0.0061,0.0028</t>
+  </si>
+  <si>
+    <t>0.9723,0.0234,0.0056,0.0010</t>
+  </si>
+  <si>
+    <t>0.9754,0.0154,0.0047,0.0026</t>
+  </si>
+  <si>
+    <t>0.9541,0.0306,0.0176,0.0034</t>
+  </si>
+  <si>
+    <t>0.9751,0.0156,0.0082,0.0008</t>
+  </si>
+  <si>
+    <t>0.9066,0.1167,0.0128,0.0007</t>
+  </si>
+  <si>
+    <t>0.9941,0.0017,0.0004,0.0009</t>
+  </si>
+  <si>
+    <t>0.4658,0.6118,0.0081,0.0041</t>
+  </si>
+  <si>
+    <t>0.2715,0.7982,0.0091,0.0027</t>
+  </si>
+  <si>
+    <t>0.2150,0.8526,0.0033,0.0016</t>
+  </si>
+  <si>
+    <t>0.0867,0.1546,0.9083,0.0031</t>
+  </si>
+  <si>
+    <t>0.9264,0.0716,0.0137,0.0017</t>
+  </si>
+  <si>
+    <t>0.7246,0.2573,0.0685,0.0023</t>
+  </si>
+  <si>
+    <t>0.8950,0.0748,0.0354,0.0037</t>
+  </si>
+  <si>
+    <t>0.9106,0.0710,0.0246,0.0018</t>
+  </si>
+  <si>
+    <t>0.0049,0.0239,0.9926,0.0013</t>
+  </si>
+  <si>
+    <t>0.8943,0.0735,0.0362,0.0034</t>
+  </si>
+  <si>
+    <t>0.0095,0.0095,0.9910,0.0004</t>
+  </si>
+  <si>
+    <t>0.0045,0.0673,0.9842,0.0017</t>
+  </si>
+  <si>
+    <t>0.0285,0.0395,0.9536,0.0039</t>
+  </si>
+  <si>
+    <t>0.0149,0.2297,0.9266,0.0019</t>
+  </si>
+  <si>
+    <t>0.0299,0.0207,0.9747,0.0004</t>
+  </si>
+  <si>
+    <t>0.0009,0.0037,0.9978,0.0007</t>
+  </si>
+  <si>
+    <t>0.0441,0.0586,0.9150,0.0015</t>
+  </si>
+  <si>
+    <t>0.1282,0.2050,0.7729,0.0069</t>
+  </si>
+  <si>
+    <t>0.3108,0.3967,0.3093,0.0244</t>
+  </si>
+  <si>
+    <t>0.4673,0.0740,0.5610,0.0160</t>
+  </si>
+  <si>
+    <t>0.4078,0.2457,0.3151,0.0041</t>
+  </si>
+  <si>
+    <t>0.1681,0.2309,0.5097,0.0008</t>
+  </si>
+  <si>
+    <t>0.6784,0.0596,0.2329,0.0005</t>
+  </si>
+  <si>
+    <t>0.5831,0.0522,0.4407,0.0031</t>
+  </si>
+  <si>
+    <t>0.2478,0.1056,0.6975,0.0105</t>
+  </si>
+  <si>
+    <t>0.5536,0.4622,0.0542,0.0029</t>
+  </si>
+  <si>
+    <t>0.5472,0.6433,0.0055,0.0009</t>
+  </si>
+  <si>
+    <t>0.6923,0.4102,0.0173,0.0021</t>
+  </si>
+  <si>
+    <t>0.9696,0.0374,0.0025,0.0010</t>
+  </si>
+  <si>
+    <t>0.0846,0.9221,0.0066,0.0040</t>
+  </si>
+  <si>
+    <t>0.5972,0.0585,0.3380,0.0789</t>
+  </si>
+  <si>
+    <t>0.8059,0.0152,0.2421,0.0063</t>
+  </si>
+  <si>
+    <t>0.2737,0.3518,0.3973,0.0736</t>
+  </si>
+  <si>
+    <t>0.7732,0.0129,0.2253,0.0135</t>
+  </si>
+  <si>
+    <t>0.5779,0.1888,0.2380,0.0407</t>
+  </si>
+  <si>
+    <t>0.1898,0.1075,0.7571,0.0307</t>
+  </si>
+  <si>
+    <t>0.2413,0.1470,0.6594,0.0496</t>
+  </si>
+  <si>
+    <t>0.0541,0.2061,0.8252,0.0464</t>
+  </si>
+  <si>
+    <t>0.0648,0.0237,0.9305,0.0059</t>
+  </si>
+  <si>
+    <t>0.0904,0.4176,0.7479,0.0292</t>
+  </si>
+  <si>
+    <t>0.9672,0.0207,0.0100,0.0018</t>
+  </si>
+  <si>
+    <t>0.9642,0.0237,0.0020,0.0042</t>
+  </si>
+  <si>
+    <t>0.9691,0.0243,0.0028,0.0025</t>
+  </si>
+  <si>
+    <t>0.9706,0.0322,0.0057,0.0005</t>
+  </si>
+  <si>
+    <t>0.9770,0.0221,0.0021,0.0010</t>
+  </si>
+  <si>
+    <t>0.9838,0.0182,0.0023,0.0001</t>
+  </si>
+  <si>
+    <t>0.9891,0.0028,0.0004,0.0027</t>
+  </si>
+  <si>
+    <t>0.9714,0.0226,0.0045,0.0017</t>
+  </si>
+  <si>
+    <t>0.1879,0.0121,0.9084,0.0018</t>
+  </si>
+  <si>
+    <t>0.3802,0.3697,0.3821,0.0313</t>
+  </si>
+  <si>
+    <t>0.7211,0.0848,0.1482,0.0924</t>
+  </si>
+  <si>
+    <t>0.0034,0.0124,0.9917,0.0013</t>
+  </si>
+  <si>
+    <t>0.0083,0.0549,0.9741,0.0047</t>
+  </si>
+  <si>
+    <t>0.0134,0.0911,0.9417,0.0003</t>
+  </si>
+  <si>
+    <t>0.0004,0.0073,0.9978,0.0009</t>
+  </si>
+  <si>
+    <t>0.0148,0.0145,0.9824,0.0012</t>
+  </si>
+  <si>
+    <t>0.0020,0.0045,0.9957,0.0011</t>
+  </si>
+  <si>
+    <t>0.0056,0.0814,0.9643,0.0081</t>
+  </si>
+  <si>
+    <t>0.2834,0.0690,0.6963,0.0065</t>
+  </si>
+  <si>
+    <t>0.7021,0.0035,0.3945,0.0119</t>
+  </si>
+  <si>
+    <t>0.6289,0.0082,0.5523,0.0081</t>
+  </si>
+  <si>
+    <t>0.7594,0.0035,0.2425,0.0230</t>
+  </si>
+  <si>
+    <t>0.9348,0.0618,0.0170,0.0009</t>
+  </si>
+  <si>
+    <t>0.9899,0.0088,0.0002,0.0005</t>
+  </si>
+  <si>
+    <t>0.9916,0.0065,0.0011,0.0002</t>
+  </si>
+  <si>
+    <t>0.9389,0.0776,0.0053,0.0015</t>
+  </si>
+  <si>
+    <t>0.9778,0.0202,0.0017,0.0017</t>
+  </si>
+  <si>
+    <t>0.9862,0.0090,0.0008,0.0005</t>
+  </si>
+  <si>
+    <t>0.9894,0.0061,0.0006,0.0007</t>
+  </si>
+  <si>
+    <t>0.9794,0.0165,0.0015,0.0018</t>
+  </si>
+  <si>
+    <t>0.0333,0.1483,0.9088,0.0023</t>
+  </si>
+  <si>
+    <t>0.0024,0.0171,0.9918,0.0026</t>
+  </si>
+  <si>
+    <t>0.0153,0.0325,0.9667,0.0023</t>
+  </si>
+  <si>
+    <t>0.0320,0.6628,0.3205,0.0996</t>
+  </si>
+  <si>
+    <t>0.0157,0.0231,0.9705,0.0032</t>
+  </si>
+  <si>
+    <t>0.1618,0.0018,0.2972,0.4881</t>
+  </si>
+  <si>
+    <t>0.0941,0.0229,0.8915,0.0175</t>
+  </si>
+  <si>
+    <t>0.0278,0.2869,0.8884,0.0186</t>
+  </si>
+  <si>
+    <t>0.5028,0.0007,0.0046,0.6471</t>
+  </si>
+  <si>
+    <t>0.0100,0.0591,0.0018,0.9919</t>
+  </si>
+  <si>
+    <t>0.0316,0.0049,0.0014,0.9873</t>
+  </si>
+  <si>
+    <t>0.0136,0.0005,0.0057,0.9883</t>
+  </si>
+  <si>
+    <t>0.0010,0.0008,0.0004,0.9992</t>
+  </si>
+  <si>
+    <t>0.6270,0.0649,0.0783,0.2495</t>
   </si>
 </sst>
 </file>
@@ -1956,10 +1965,10 @@
         <v>259</v>
       </c>
       <c r="C2" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D2" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1973,7 +1982,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1984,10 +1993,10 @@
         <v>259</v>
       </c>
       <c r="C4" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -2001,7 +2010,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2015,7 +2024,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2029,7 +2038,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2043,7 +2052,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2057,7 +2066,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2071,7 +2080,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2085,7 +2094,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2099,7 +2108,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2113,7 +2122,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2124,10 +2133,10 @@
         <v>259</v>
       </c>
       <c r="C14" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D14" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2141,7 +2150,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2155,7 +2164,7 @@
         <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2169,7 +2178,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2183,7 +2192,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2197,7 +2206,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2211,7 +2220,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2225,7 +2234,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2239,7 +2248,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2253,7 +2262,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2264,10 +2273,10 @@
         <v>259</v>
       </c>
       <c r="C24" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D24" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2278,10 +2287,10 @@
         <v>259</v>
       </c>
       <c r="C25" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D25" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2295,7 +2304,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2309,7 +2318,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2323,7 +2332,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2337,7 +2346,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2351,7 +2360,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2362,10 +2371,10 @@
         <v>259</v>
       </c>
       <c r="C31" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D31" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2379,7 +2388,7 @@
         <v>261</v>
       </c>
       <c r="D32" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2393,7 +2402,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2407,7 +2416,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2421,7 +2430,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2435,7 +2444,7 @@
         <v>259</v>
       </c>
       <c r="D36" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2446,10 +2455,10 @@
         <v>259</v>
       </c>
       <c r="C37" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D37" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2463,7 +2472,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2474,10 +2483,10 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D39" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2488,10 +2497,10 @@
         <v>261</v>
       </c>
       <c r="C40" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D40" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2502,10 +2511,10 @@
         <v>261</v>
       </c>
       <c r="C41" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2519,7 +2528,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2533,7 +2542,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2547,7 +2556,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2561,7 +2570,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2572,10 +2581,10 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="D46" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2589,7 +2598,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2603,7 +2612,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2617,7 +2626,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2628,10 +2637,10 @@
         <v>261</v>
       </c>
       <c r="C50" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2645,7 +2654,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2659,7 +2668,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2673,7 +2682,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2687,7 +2696,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2698,10 +2707,10 @@
         <v>261</v>
       </c>
       <c r="C55" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2715,7 +2724,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2729,7 +2738,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2743,7 +2752,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2757,7 +2766,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2771,7 +2780,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2785,7 +2794,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2796,10 +2805,10 @@
         <v>259</v>
       </c>
       <c r="C62" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2813,7 +2822,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2827,7 +2836,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2841,7 +2850,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2855,7 +2864,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2869,7 +2878,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2883,7 +2892,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2897,7 +2906,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2908,10 +2917,10 @@
         <v>259</v>
       </c>
       <c r="C70" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2925,7 +2934,7 @@
         <v>261</v>
       </c>
       <c r="D71" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2936,10 +2945,10 @@
         <v>261</v>
       </c>
       <c r="C72" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D72" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2950,10 +2959,10 @@
         <v>263</v>
       </c>
       <c r="C73" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2967,7 +2976,7 @@
         <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2981,7 +2990,7 @@
         <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2995,7 +3004,7 @@
         <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3009,7 +3018,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3023,7 +3032,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3037,7 +3046,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3051,7 +3060,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3065,7 +3074,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3079,7 +3088,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3093,7 +3102,7 @@
         <v>262</v>
       </c>
       <c r="D83" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3104,10 +3113,10 @@
         <v>261</v>
       </c>
       <c r="C84" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D84" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3121,7 +3130,7 @@
         <v>262</v>
       </c>
       <c r="D85" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3132,10 +3141,10 @@
         <v>263</v>
       </c>
       <c r="C86" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D86" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3149,7 +3158,7 @@
         <v>262</v>
       </c>
       <c r="D87" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3160,10 +3169,10 @@
         <v>262</v>
       </c>
       <c r="C88" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D88" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3177,7 +3186,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3191,7 +3200,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3205,7 +3214,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3219,7 +3228,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3233,7 +3242,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3247,7 +3256,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3261,7 +3270,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3275,7 +3284,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3289,7 +3298,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3303,7 +3312,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3317,7 +3326,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3331,7 +3340,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3345,7 +3354,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3359,7 +3368,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3373,7 +3382,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3387,7 +3396,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3401,7 +3410,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3415,7 +3424,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3426,10 +3435,10 @@
         <v>259</v>
       </c>
       <c r="C107" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D107" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3443,7 +3452,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3457,7 +3466,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3471,7 +3480,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3485,7 +3494,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3499,7 +3508,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3513,7 +3522,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3527,7 +3536,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3541,7 +3550,7 @@
         <v>262</v>
       </c>
       <c r="D115" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3555,7 +3564,7 @@
         <v>259</v>
       </c>
       <c r="D116" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3569,7 +3578,7 @@
         <v>261</v>
       </c>
       <c r="D117" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3580,10 +3589,10 @@
         <v>259</v>
       </c>
       <c r="C118" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D118" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3594,10 +3603,10 @@
         <v>261</v>
       </c>
       <c r="C119" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D119" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3611,7 +3620,7 @@
         <v>260</v>
       </c>
       <c r="D120" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3625,7 +3634,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3639,7 +3648,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3653,7 +3662,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3667,7 +3676,7 @@
         <v>262</v>
       </c>
       <c r="D124" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3681,7 +3690,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3695,7 +3704,7 @@
         <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3709,7 +3718,7 @@
         <v>262</v>
       </c>
       <c r="D127" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3723,7 +3732,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3737,7 +3746,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3751,7 +3760,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3765,7 +3774,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3779,7 +3788,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3793,7 +3802,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3807,7 +3816,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3821,7 +3830,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3835,7 +3844,7 @@
         <v>263</v>
       </c>
       <c r="D136" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3846,10 +3855,10 @@
         <v>261</v>
       </c>
       <c r="C137" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D137" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3863,7 +3872,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3877,7 +3886,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3891,7 +3900,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3902,10 +3911,10 @@
         <v>259</v>
       </c>
       <c r="C141" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D141" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3919,7 +3928,7 @@
         <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3933,7 +3942,7 @@
         <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3947,7 +3956,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3961,7 +3970,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3975,7 +3984,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3989,7 +3998,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -4000,10 +4009,10 @@
         <v>263</v>
       </c>
       <c r="C148" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D148" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4017,7 +4026,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4031,7 +4040,7 @@
         <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4045,7 +4054,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4056,10 +4065,10 @@
         <v>262</v>
       </c>
       <c r="C152" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D152" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4073,7 +4082,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4084,10 +4093,10 @@
         <v>259</v>
       </c>
       <c r="C154" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D154" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4101,7 +4110,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4115,7 +4124,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4129,7 +4138,7 @@
         <v>260</v>
       </c>
       <c r="D157" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4143,7 +4152,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4157,7 +4166,7 @@
         <v>262</v>
       </c>
       <c r="D159" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4171,7 +4180,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4185,7 +4194,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4199,7 +4208,7 @@
         <v>262</v>
       </c>
       <c r="D162" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4210,10 +4219,10 @@
         <v>259</v>
       </c>
       <c r="C163" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D163" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4227,7 +4236,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4241,7 +4250,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4255,7 +4264,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4269,7 +4278,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4283,7 +4292,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4297,7 +4306,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4311,7 +4320,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4325,7 +4334,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4339,7 +4348,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4353,7 +4362,7 @@
         <v>262</v>
       </c>
       <c r="D173" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4367,7 +4376,7 @@
         <v>262</v>
       </c>
       <c r="D174" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4381,7 +4390,7 @@
         <v>262</v>
       </c>
       <c r="D175" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4392,10 +4401,10 @@
         <v>261</v>
       </c>
       <c r="C176" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D176" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4409,7 +4418,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4423,7 +4432,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4437,7 +4446,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4451,7 +4460,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4465,7 +4474,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4479,7 +4488,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4493,7 +4502,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4507,7 +4516,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4521,7 +4530,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4535,7 +4544,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4549,7 +4558,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4563,7 +4572,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4577,7 +4586,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4591,7 +4600,7 @@
         <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4602,10 +4611,10 @@
         <v>259</v>
       </c>
       <c r="C191" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D191" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4619,7 +4628,7 @@
         <v>261</v>
       </c>
       <c r="D192" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4630,10 +4639,10 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D193" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4647,7 +4656,7 @@
         <v>261</v>
       </c>
       <c r="D194" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4661,7 +4670,7 @@
         <v>259</v>
       </c>
       <c r="D195" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4675,7 +4684,7 @@
         <v>259</v>
       </c>
       <c r="D196" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4689,7 +4698,7 @@
         <v>261</v>
       </c>
       <c r="D197" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4703,7 +4712,7 @@
         <v>259</v>
       </c>
       <c r="D198" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4714,10 +4723,10 @@
         <v>262</v>
       </c>
       <c r="C199" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="D199" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4728,10 +4737,10 @@
         <v>262</v>
       </c>
       <c r="C200" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D200" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4745,7 +4754,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4756,10 +4765,10 @@
         <v>259</v>
       </c>
       <c r="C202" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D202" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4773,7 +4782,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4787,7 +4796,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4798,10 +4807,10 @@
         <v>259</v>
       </c>
       <c r="C205" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D205" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4812,10 +4821,10 @@
         <v>261</v>
       </c>
       <c r="C206" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D206" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4829,7 +4838,7 @@
         <v>259</v>
       </c>
       <c r="D207" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4843,7 +4852,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4857,7 +4866,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4871,7 +4880,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4885,7 +4894,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4899,7 +4908,7 @@
         <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4913,7 +4922,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4927,7 +4936,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4941,7 +4950,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4955,7 +4964,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4969,7 +4978,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4983,7 +4992,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4997,7 +5006,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5011,7 +5020,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5025,7 +5034,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5036,10 +5045,10 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D222" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5053,7 +5062,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5067,7 +5076,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5081,7 +5090,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5095,7 +5104,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5109,7 +5118,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5123,7 +5132,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5137,7 +5146,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5151,7 +5160,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5165,7 +5174,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5179,7 +5188,7 @@
         <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5190,10 +5199,10 @@
         <v>259</v>
       </c>
       <c r="C233" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D233" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5207,7 +5216,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5221,7 +5230,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5235,7 +5244,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5249,7 +5258,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5263,7 +5272,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5277,7 +5286,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5291,7 +5300,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5305,7 +5314,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5319,7 +5328,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5333,7 +5342,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5347,7 +5356,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5361,7 +5370,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5372,10 +5381,10 @@
         <v>261</v>
       </c>
       <c r="C246" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D246" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5389,7 +5398,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5400,10 +5409,10 @@
         <v>261</v>
       </c>
       <c r="C248" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D248" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5417,7 +5426,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5431,7 +5440,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5442,10 +5451,10 @@
         <v>259</v>
       </c>
       <c r="C251" t="s">
-        <v>260</v>
+        <v>267</v>
       </c>
       <c r="D251" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5459,7 +5468,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5473,7 +5482,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5487,7 +5496,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5501,7 +5510,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5512,10 +5521,10 @@
         <v>259</v>
       </c>
       <c r="C256" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
     </row>
   </sheetData>
